--- a/public/bulk-upload-template.xlsx
+++ b/public/bulk-upload-template.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -485,26 +485,27 @@
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="40" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -548,102 +549,107 @@
           <t>thumbnail</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>mrp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>subCategory</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>occasions</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>countryOfOrigin</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>genericName</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>netQuantity</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>dimensions</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>finish</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>monthYearOfImport</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>featured</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>shortCaption</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>shortSticker</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>slug</t>
         </is>
@@ -678,96 +684,101 @@
           <t>krishna-flute-thumb.jpg</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>krishna-flute.mp4</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
         <v>3950</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>4500</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>pooja</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Brass Idols</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Brass Krishna standing with a flute, on a lotus base.</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>festival;wedding</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Sri Balaji Handicrafts</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>Brass idol</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>1 piece</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>9 x 4 x 3 in</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>850 g</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>Antique brass</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>09/2026</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>The one everyone asks for</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>Bestseller</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="n"/>
+      <c r="AC2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -790,98 +801,99 @@
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n">
         <v>1299</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>1799</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>bags</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Slings &amp; Crossbody</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Compact tan sling with an adjustable strap and two zip pockets.</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>birthday;everyday</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Hidesign Leathers</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>Sling bag</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>1 piece</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>10 x 7 x 3 in</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>420 g</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>Genuine leather</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>08/2026</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="L2:L5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="One of the eight section codes - see the 'Section codes' sheet." promptTitle="Pick from the list" prompt="One of the eight section codes - see the 'Section codes' sheet." type="list">
+    <dataValidation sqref="M2:M5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="One of the eight section codes - see the 'Section codes' sheet." promptTitle="Pick from the list" prompt="One of the eight section codes - see the 'Section codes' sheet." type="list">
       <formula1>"decor,pooja,fashion,bags,shoes,watches,gifting,lifestyle"</formula1>
     </dataValidation>
-    <dataValidation sqref="X2:X5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="live = on the website. draft = held back. hidden = retired." promptTitle="Pick from the list" prompt="live = on the website. draft = held back. hidden = retired." type="list">
+    <dataValidation sqref="Y2:Y5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="live = on the website. draft = held back. hidden = retired." promptTitle="Pick from the list" prompt="live = on the website. draft = held back. hidden = retired." type="list">
       <formula1>"live,draft,hidden"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="yes puts it in the Shoppable Shorts rail. Keep this to a handful." promptTitle="Pick from the list" prompt="yes puts it in the Shoppable Shorts rail. Keep this to a handful." type="list">
+    <dataValidation sqref="Z2:Z5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="yes puts it in the Shoppable Shorts rail. Keep this to a handful." promptTitle="Pick from the list" prompt="yes puts it in the Shoppable Shorts rail. Keep this to a handful." type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1021,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -1120,36 +1132,40 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - 1600 x 2000 pixels (portrait, 4:5), JPG, under 1 MB each.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - photo_1 must be clean: no price, no text. Sizes and prices go on the last photo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>THUMBNAIL - the picture in the shop grid</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>A SEPARATE image, not one of the photos above. It is the one picture a customer sees</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>while browsing, before they click in - so it is the one that sells the product.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">      thumbnail   krishna-flute-thumb.jpg</t>
+          <t>while browsing, before they click in - so it is the one that sells the product.</t>
         </is>
       </c>
     </row>
@@ -1159,171 +1175,232 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - It goes in the same folder as the photos.</t>
+          <t xml:space="preserve">      thumbnail   krishna-flute-thumb.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - Name it after the product with -thumb on the end.</t>
-        </is>
-      </c>
+      <c r="A25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - Roughly square works best. The grid crops to a square.</t>
+          <t xml:space="preserve">      - It goes in the same folder as the photos.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">      - Name it after the product with -thumb on the end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - 1600 x 2000 pixels, like the photos. The grid shows it at 4:5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">      - LEAVE IT BLANK and photo_1 is used instead. That is fine.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>FILENAME RULES - the part nobody can fix afterwards</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - No spaces. Use hyphens.</t>
-        </is>
-      </c>
+      <c r="A30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - Every filename in the sheet must be in the folder, spelled exactly the same.</t>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>VIDEO - optional, one per product</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Krishna-Flute-01.JPG and krishna-flute-01.jpg are different files.</t>
+          <t>Shown second on the product page, right after photo_1, and plays by itself (silent).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - Send the images that come out of the ChatGPT step, not the originals off the phone.</t>
-        </is>
-      </c>
+      <c r="A33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr"/>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      video   krishna-flute.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>THE FIDDLY COLUMNS</t>
-        </is>
-      </c>
+      <c r="A35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>price, mrp, stock   Numbers only. 3950, never Rs 3,950. mrp is the struck-through price.</t>
+          <t xml:space="preserve">      - MP4, vertical 9:16 (1080 x 1920), 15 to 30 seconds, under 50 MB.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>category            Pick from the dropdown. Codes are on the 'Section codes' sheet.</t>
+          <t xml:space="preserve">      - Same folder as the photos. Name it after the product.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>subCategory         Your own grouping, e.g. 'Brass Idols'. Spell it the same way every time.</t>
+          <t xml:space="preserve">      - No price or text on it, and no songs from Instagram or other apps.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>occasions           Any of: birthday, wedding, festival, everyday - semicolons between them.</t>
-        </is>
-      </c>
+      <c r="A39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>status              live = on the website now. draft = ready but held back. hidden = retired.</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>FILENAME RULES - the part nobody can fix afterwards</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>featured            yes puts it in the Shoppable Shorts rail. A handful only.</t>
+          <t xml:space="preserve">      - No spaces. Use hyphens.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>slug                LEAVE BLANK. It is the product's web address, filled in automatically.</t>
+          <t xml:space="preserve">      - Every filename in the sheet must be in the folder, spelled exactly the same.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    Only filled for products that already exist, so their links keep working.</t>
+          <t xml:space="preserve">        Krishna-Flute-01.JPG and krishna-flute-01.jpg are different files.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr"/>
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Send the images that come out of the ChatGPT step, not the originals off the phone.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>UPLOADING THE SAME SHEET TWICE IS SAFE</t>
-        </is>
-      </c>
+      <c r="A45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>A product that already exists is updated, not copied. So you can fix a price in the sheet</t>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>THE FIDDLY COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>and upload it again.</t>
+          <t>price, mrp, stock   Numbers only. 3950, never Rs 3,950. mrp is the struck-through price.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr"/>
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>category            Pick from the dropdown. Codes are on the 'Section codes' sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>SEND THE FIRST FIFTY FIRST.</t>
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>subCategory         Your own grouping, e.g. 'Brass Idols'. Spell it the same way every time.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>occasions           Any of: birthday, wedding, festival, everyday - semicolons between them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>status              live = on the website now. draft = ready but held back. hidden = retired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>featured            yes puts it in the Shoppable Shorts rail. A handful only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>slug                LEAVE BLANK. It is the product's web address, filled in automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    Only filled for products that already exist, so their links keep working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>UPLOADING THE SAME SHEET TWICE IS SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>A product that already exists is updated, not copied. So you can fix a price in the sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>and upload it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>SEND THE FIRST FIFTY FIRST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>A mistake caught on fifty rows costs an hour. Caught on a thousand, it costs a week.</t>
         </is>
